--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/20. СТО Каприз (ИП Новик В.В.)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/20. СТО Каприз (ИП Новик В.В.)/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92564006482</v>
+        <v>46157.93082444756</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/20. СТО Каприз (ИП Новик В.В.)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/20. СТО Каприз (ИП Новик В.В.)/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93082444756</v>
+        <v>46157.9316151819</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/20. СТО Каприз (ИП Новик В.В.)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/20. СТО Каприз (ИП Новик В.В.)/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9316151819</v>
+        <v>46157.93396069916</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/20. СТО Каприз (ИП Новик В.В.)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/20. СТО Каприз (ИП Новик В.В.)/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93396069916</v>
+        <v>46157.93713089947</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/20. СТО Каприз (ИП Новик В.В.)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/20. СТО Каприз (ИП Новик В.В.)/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93713089947</v>
+        <v>46158.282125928</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/20. СТО Каприз (ИП Новик В.В.)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/20. СТО Каприз (ИП Новик В.В.)/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.282125928</v>
+        <v>46158.29673754646</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/20. СТО Каприз (ИП Новик В.В.)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/20. СТО Каприз (ИП Новик В.В.)/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29673754646</v>
+        <v>46158.29809632836</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/20. СТО Каприз (ИП Новик В.В.)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/20. СТО Каприз (ИП Новик В.В.)/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29809632836</v>
+        <v>46158.33383402287</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/20. СТО Каприз (ИП Новик В.В.)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/20. СТО Каприз (ИП Новик В.В.)/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33383402287</v>
+        <v>46158.36851690553</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/20. СТО Каприз (ИП Новик В.В.)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/20. СТО Каприз (ИП Новик В.В.)/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36851690553</v>
+        <v>46158.37283623775</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
